--- a/Production/Reference_Board/Reference_Board.xlsx
+++ b/Production/Reference_Board/Reference_Board.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kim/Desktop/Lab/Github/PyOpticL_Rubidium_System/Production/ReferenceBoard/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kim/Desktop/Lab/Sinclair/pyopticl-setups/Production/Reference_Board/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2391E5FE-78D7-B84D-9CF8-934AEFF2156B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61E575ED-06A1-F041-ADFF-7C9B51900314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19400" yWindow="740" windowWidth="10000" windowHeight="16680" xr2:uid="{42F6A15E-87CE-9147-9545-45C46C70D310}"/>
+    <workbookView xWindow="14700" yWindow="660" windowWidth="14700" windowHeight="16680" xr2:uid="{42F6A15E-87CE-9147-9545-45C46C70D310}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
   <si>
     <t>Reference Board</t>
   </si>
@@ -86,13 +86,31 @@
   </si>
   <si>
     <t>Reference_Baseplate.step</t>
+  </si>
+  <si>
+    <t>C060TMD-B</t>
+  </si>
+  <si>
+    <t>Elements</t>
+  </si>
+  <si>
+    <t>Optics</t>
+  </si>
+  <si>
+    <t>QWP</t>
+  </si>
+  <si>
+    <t>HWP</t>
+  </si>
+  <si>
+    <t>PBS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -106,6 +124,13 @@
       <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -130,9 +155,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -468,19 +494,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{504A0317-4413-EE44-9F8B-28AC1E65744B}">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B3" t="s">
@@ -535,6 +561,14 @@
         <v>1</v>
       </c>
     </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2</v>
+      </c>
+    </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>11</v>
@@ -561,7 +595,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B16">
         <v>7</v>
@@ -569,7 +603,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B17">
         <v>7</v>
@@ -577,7 +611,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B18">
         <v>7</v>
@@ -585,30 +619,71 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B19">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20">
+      <c r="B26">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27">
         <v>7</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A17" r:id="rId1" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=SM05L05" xr:uid="{26D03288-5EB5-E849-A9E7-78F166728512}"/>
-    <hyperlink ref="A18" r:id="rId2" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=SM05FCA2" xr:uid="{7396B97A-1E53-F246-B983-DFB7235DDE2B}"/>
+    <hyperlink ref="A16" r:id="rId1" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=SM05L05" xr:uid="{26D03288-5EB5-E849-A9E7-78F166728512}"/>
+    <hyperlink ref="A17" r:id="rId2" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=SM05FCA2" xr:uid="{7396B97A-1E53-F246-B983-DFB7235DDE2B}"/>
     <hyperlink ref="A15" r:id="rId3" xr:uid="{1BBCBD75-E5E4-9C42-9870-10D5AFE8751D}"/>
     <hyperlink ref="A13" r:id="rId4" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=RSP05" xr:uid="{8DD89EFB-A6D7-DC45-81DC-A3DF706D2C18}"/>
     <hyperlink ref="A14" r:id="rId5" xr:uid="{27DD0994-D2B1-854C-8165-72C16DCFC984}"/>
-    <hyperlink ref="A19" r:id="rId6" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=BB05-E03" xr:uid="{A85C602C-A7C0-4B48-94F9-6B38884C0FD3}"/>
-    <hyperlink ref="A20" r:id="rId7" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=S05TM09" xr:uid="{EF391373-8D5D-B54F-B9A3-5D87DFC3B5D2}"/>
-    <hyperlink ref="A16" r:id="rId8" xr:uid="{2C39C91F-698E-3046-B84D-D54EF6E620B0}"/>
+    <hyperlink ref="A26" r:id="rId6" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=BB05-E03" xr:uid="{A85C602C-A7C0-4B48-94F9-6B38884C0FD3}"/>
+    <hyperlink ref="A18" r:id="rId7" display="https://www.thorlabs.com/thorproduct.cfm?partnumber=S05TM09" xr:uid="{EF391373-8D5D-B54F-B9A3-5D87DFC3B5D2}"/>
+    <hyperlink ref="A19" r:id="rId8" xr:uid="{2C39C91F-698E-3046-B84D-D54EF6E620B0}"/>
+    <hyperlink ref="A25" r:id="rId9" xr:uid="{51F1016B-56DB-0242-B2A9-A6D1B04C4A0E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
